--- a/data/trans_camb/P1417-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P1417-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,08</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>3,9</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 0,73</t>
+          <t>-0,69; 0,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 1,83</t>
+          <t>-0,12; 1,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,73</t>
+          <t>1,85; 4,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,73</t>
+          <t>-0,04; 2,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 2,85</t>
+          <t>-0,2; 2,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,97</t>
+          <t>2,89; 6,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 1,65</t>
+          <t>-0,09; 1,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,99</t>
+          <t>0,19; 2,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,83; 4,96</t>
+          <t>2,85; 5,0</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>526,73%</t>
+          <t>506,16%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>180,59%</t>
+          <t>183,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>244,18%</t>
+          <t>242,13%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-78,9; 300,71</t>
+          <t>-73,21; 308,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-34,14; 604,82</t>
+          <t>-23,8; 586,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>145,14; 1542,42</t>
+          <t>153,39; 1639,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 146,82</t>
+          <t>-4,13; 149,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 156,19</t>
+          <t>-11,28; 144,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,78; 327,9</t>
+          <t>89,96; 344,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 128,69</t>
+          <t>-7,07; 130,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,26; 164,81</t>
+          <t>7,06; 164,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>138,66; 399,34</t>
+          <t>142,98; 424,05</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,62</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,14</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,54</t>
+          <t>-0,21; 0,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,49</t>
+          <t>-0,27; 0,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 0,91</t>
+          <t>0,19; 1,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,73</t>
+          <t>0,01; 1,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,58</t>
+          <t>-0,04; 1,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,18</t>
+          <t>1,76; 3,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 0,96</t>
+          <t>-0,02; 0,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 0,92</t>
+          <t>-0,03; 0,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,9</t>
+          <t>1,07; 2,17</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185,19%</t>
+          <t>234,74%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>167,31%</t>
+          <t>204,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>174,15%</t>
+          <t>214,03%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,5; 472,99</t>
+          <t>-60,96; 546,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-63,01; 435,41</t>
+          <t>-71,33; 518,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,5; 668,91</t>
+          <t>26,14; 962,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 191,81</t>
+          <t>-1,4; 192,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 175,38</t>
+          <t>-4,92; 175,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,48; 362,6</t>
+          <t>96,84; 408,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 169,34</t>
+          <t>-4,7; 159,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 171,7</t>
+          <t>-4,92; 158,52</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,81; 349,8</t>
+          <t>103,85; 396,81</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,64</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,27</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,43</t>
+          <t>-1,4; 0,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,25</t>
+          <t>-1,5; 0,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 0,35</t>
+          <t>-1,3; 0,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,84</t>
+          <t>-0,77; 2,64</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 2,43</t>
+          <t>-0,94; 2,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,35</t>
+          <t>0,95; 4,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,26</t>
+          <t>-0,61; 1,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 1,18</t>
+          <t>-0,76; 1,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,24</t>
+          <t>0,28; 2,13</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-41,12%</t>
+          <t>-42,37%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>222,45%</t>
+          <t>213,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>156,78%</t>
+          <t>150,92%</t>
         </is>
       </c>
     </row>
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,35; 530,07</t>
+          <t>-45,59; 482,89</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,45; 487,61</t>
+          <t>-55,81; 401,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,13; 915,58</t>
+          <t>23,41; 853,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,2; 284,93</t>
+          <t>-52,26; 271,79</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,84; 266,92</t>
+          <t>-62,81; 272,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,6; 586,81</t>
+          <t>8,53; 510,7</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,49</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,85</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 0,35</t>
+          <t>-0,31; 0,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,53</t>
+          <t>-0,18; 0,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,12</t>
+          <t>0,39; 1,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,77</t>
+          <t>0,29; 1,73</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,47</t>
+          <t>0,09; 1,43</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 3,36</t>
+          <t>2,07; 3,53</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,95</t>
+          <t>0,12; 0,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,86</t>
+          <t>0,07; 0,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 2,13</t>
+          <t>1,41; 2,32</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>172,2%</t>
+          <t>196,59%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>145,98%</t>
+          <t>165,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>152,77%</t>
+          <t>173,21%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-50,55; 130,56</t>
+          <t>-52,34; 122,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-34,36; 211,46</t>
+          <t>-36,19; 196,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44,25; 468,74</t>
+          <t>46,49; 436,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15,8; 128,81</t>
+          <t>12,63; 124,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,33; 106,95</t>
+          <t>2,72; 101,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>77,27; 248,86</t>
+          <t>100,34; 262,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,86; 106,9</t>
+          <t>9,24; 107,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>7,45; 98,44</t>
+          <t>5,23; 101,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>88,3; 240,82</t>
+          <t>109,7; 262,54</t>
         </is>
       </c>
     </row>
